--- a/src/src/main/resources/report/workOrderScript.xlsx
+++ b/src/src/main/resources/report/workOrderScript.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503248825.HCAD\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050B5C4B-5FC8-4531-9CB6-55841A59A583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06570CDA-6716-48A7-A0E0-8FDA8B4F773A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28365" yWindow="-16320" windowWidth="29040" windowHeight="15225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-435" yWindow="-16500" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="2" r:id="rId1"/>
@@ -48,15 +48,9 @@
     <t>case_priority</t>
   </si>
   <si>
-    <t>紧急程度</t>
-  </si>
-  <si>
     <t>request_reason</t>
   </si>
   <si>
-    <t>原因</t>
-  </si>
-  <si>
     <t>[1,2,3]</t>
   </si>
   <si>
@@ -66,28 +60,9 @@
     <t>fe_uid</t>
   </si>
   <si>
-    <t>待派工大于最大值的按照时间派工</t>
-  </si>
-  <si>
-    <t>随机派给工程师</t>
-  </si>
-  <si>
-    <t>超过最大值不产生新工单
-小于最大值产生max-n 条工单</t>
-  </si>
-  <si>
-    <t>报修设备列表</t>
-  </si>
-  <si>
-    <t>报修人列表</t>
-  </si>
-  <si>
     <t>大于最大值的维修完成</t>
   </si>
   <si>
-    <t>大于最大值的完成验收</t>
-  </si>
-  <si>
     <t>057fdd13412e46df891762c01f526846</t>
   </si>
   <si>
@@ -115,15 +90,9 @@
     <t>man_hours</t>
   </si>
   <si>
-    <t>大于最大值的完成关单</t>
-  </si>
-  <si>
     <t>工时</t>
   </si>
   <si>
-    <t>["血氧测量不出","故障:加热器垫，组织脱水程序中断，影响组织标本","788888888888"]</t>
-  </si>
-  <si>
     <t>["9f5af592d7224f1981c28488fc30d401","978ff50a326742b19f3456f762401219","78c646a38ac64bf3a767db319e5fc7c4"]</t>
   </si>
   <si>
@@ -131,25 +100,49 @@
   </si>
   <si>
     <t>["86d38945ed394530bee1f5c7a5e88861","214b05ecb78c46fcbec39ab97ef7000e"]</t>
+  </si>
+  <si>
+    <t>["血氧测量不出","故障:加热器垫，组织脱水程序中断，影响组织标本"]</t>
+  </si>
+  <si>
+    <t>租户待办工单统计值n超过最大值不产生新工单；小于最大值产生max-n 条工单</t>
+  </si>
+  <si>
+    <t>报修设备列表，添加资产uid</t>
+  </si>
+  <si>
+    <t>报修人列表，添加用户uid</t>
+  </si>
+  <si>
+    <t>原因，支持添加报修原因</t>
+  </si>
+  <si>
+    <t>紧急程度，固定值，不支持添加</t>
+  </si>
+  <si>
+    <t>待派工工单大于最大值的按照时间派工</t>
+  </si>
+  <si>
+    <t>随机派给工程师，添加工程师用户uid</t>
+  </si>
+  <si>
+    <t>大于最大值的工单完成验收</t>
+  </si>
+  <si>
+    <t>大于最大值工单的完成关单</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF7A7E85"/>
-      <name val="Courier New"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -172,15 +165,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -473,10 +465,10 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -490,20 +482,20 @@
   <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="15.1484375" customWidth="1"/>
-    <col min="2" max="2" width="170.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.69921875" customWidth="1"/>
     <col min="4" max="4" width="17.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="42.3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2">
         <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.5">
@@ -511,13 +503,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.5">
@@ -525,27 +517,27 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
         <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.5">
@@ -553,13 +545,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -573,30 +565,30 @@
   <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="17.3984375" customWidth="1"/>
-    <col min="2" max="2" width="121.34765625" customWidth="1"/>
-    <col min="3" max="3" width="19.546875" customWidth="1"/>
+    <col min="2" max="2" width="100.046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
         <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -610,19 +602,19 @@
   <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="16.046875" customWidth="1"/>
-    <col min="2" max="2" width="37.34765625" customWidth="1"/>
-    <col min="3" max="3" width="44.25" customWidth="1"/>
+    <col min="2" max="2" width="4.19921875" customWidth="1"/>
+    <col min="3" max="3" width="27.546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -636,41 +628,41 @@
   <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="21.69921875" customWidth="1"/>
-    <col min="2" max="2" width="88.25" customWidth="1"/>
+    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="2">
+      <c r="A1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="4">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>16</v>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +689,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +715,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/resources/report/workOrderScript.xlsx
+++ b/src/src/main/resources/report/workOrderScript.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503248825.HCAD\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gehealthcare-my.sharepoint.com/personal/550004001_gehealthcare_com/Documents/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06570CDA-6716-48A7-A0E0-8FDA8B4F773A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="6_{80078819-F9C6-4EA5-A910-09A5D1CAA4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B87028CC-E773-432E-852E-9625D063F210}"/>
   <bookViews>
-    <workbookView xWindow="-435" yWindow="-16500" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,11 @@
     <sheet name="维修" sheetId="4" r:id="rId5"/>
     <sheet name="验收" sheetId="5" r:id="rId6"/>
     <sheet name="关单" sheetId="8" r:id="rId7"/>
+    <sheet name="创建保养" sheetId="9" r:id="rId8"/>
+    <sheet name="保养派工" sheetId="10" r:id="rId9"/>
+    <sheet name="保养接单" sheetId="11" r:id="rId10"/>
+    <sheet name="保养" sheetId="12" r:id="rId11"/>
+    <sheet name="保养验收" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="50">
   <si>
     <t>maxCount</t>
   </si>
@@ -130,13 +135,64 @@
   </si>
   <si>
     <t>大于最大值工单的完成关单</t>
+  </si>
+  <si>
+    <t>超过最大值不产生新工单小于最大值产生max-n 条工单</t>
+  </si>
+  <si>
+    <t>["a0c2d35d34e64374976c0d3acf0a680f","3ace74ae493a4999a9639352b5217fc1","8b5d9627cedb4c869ffefab65b92fcaf","48efc272349f48099ed2bca7beb56e2d","35751b7a493d4198901193a8ec1b7a25","0675b454dbff403f9c80dcffd459dea2"]</t>
+  </si>
+  <si>
+    <t>报修设备列表</t>
+  </si>
+  <si>
+    <t>operationUid</t>
+  </si>
+  <si>
+    <t>["e9b339f144d54e1280351fdba9ce0bbb","978ff50a326742b19f3456f762401219","78c646a38ac64bf3a767db319e5fc7c4"]</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>planTime</t>
+  </si>
+  <si>
+    <t>[1,2,6]</t>
+  </si>
+  <si>
+    <t>MaintenanceLevel</t>
+  </si>
+  <si>
+    <t>MaintenanceType</t>
+  </si>
+  <si>
+    <t>1(当前时间加一个月) ，2(当前时间加二个月) ，6(当前时间加六个月) ，</t>
+  </si>
+  <si>
+    <t>[1,2,3,4]</t>
+  </si>
+  <si>
+    <t>巡检、2级保养、3级保养、质量控制</t>
+  </si>
+  <si>
+    <t>周期、一次性、重测</t>
+  </si>
+  <si>
+    <t>待派工大于最大值的按照时间派工</t>
+  </si>
+  <si>
+    <t>随机派给工程师</t>
+  </si>
+  <si>
+    <t>大于最大值的完成验收</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -454,13 +510,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F955C69-2F55-4F2D-883C-B0C1C0B311AE}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="15.296875" customWidth="1"/>
     <col min="2" max="2" width="66.84765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -469,6 +525,80 @@
       </c>
       <c r="C1" t="s">
         <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF1973C-50E6-4A00-B8DC-F26A62C147A7}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DBEDEF6-378E-4F2D-A1AC-596FFAF640A2}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E3A7612-4547-4DE5-9EE2-DEE86FB7A1C5}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +609,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="15.1484375" customWidth="1"/>
     <col min="2" max="2" width="73.046875" bestFit="1" customWidth="1"/>
@@ -487,7 +617,7 @@
     <col min="4" max="4" width="17.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="42.3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="42.3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -498,7 +628,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -512,7 +642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -526,7 +656,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -540,7 +670,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -562,14 +692,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD8FBF4-FF1D-4E3F-A036-ECFEE3C69CC9}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="17.3984375" customWidth="1"/>
     <col min="2" max="2" width="100.046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -580,7 +710,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -599,14 +729,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{781CA063-3015-4A72-8EE5-A37AC95BE188}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="16.046875" customWidth="1"/>
     <col min="2" max="2" width="4.19921875" customWidth="1"/>
     <col min="3" max="3" width="27.546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -625,14 +755,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17C9784C-827A-4F7F-8A4B-D38B957E9679}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="21.69921875" customWidth="1"/>
     <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -643,7 +773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -654,7 +784,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
@@ -674,14 +804,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10469803-E67A-484A-984A-AB70163F90F9}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="14.3984375" customWidth="1"/>
     <col min="2" max="2" width="13.94921875" customWidth="1"/>
     <col min="3" max="3" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -700,14 +830,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5909538D-675C-4897-8866-E3A006FC8532}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -721,4 +851,131 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040A22F8-8E9F-4F70-B320-66FE63084378}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
+  <cols>
+    <col min="2" max="2" width="66.19921875" customWidth="1"/>
+    <col min="3" max="3" width="69.44921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.3" customHeight="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E065E2-B408-4875-B9F8-273CCC574685}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>